--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104469_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104469_W2.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.033200000000001</v>
+        <v>7.9707</v>
       </c>
       <c r="E2" t="n">
-        <v>8.297000000000001</v>
+        <v>7.403</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7361</v>
+        <v>0.5677</v>
       </c>
       <c r="G2" t="n">
-        <v>3.2197</v>
+        <v>3.2159</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4835</v>
+        <v>3.4702</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2638</v>
+        <v>-0.2543</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2214</v>
+        <v>4.2024</v>
       </c>
       <c r="K2" t="n">
-        <v>4.0348</v>
+        <v>4.0162</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1866</v>
+        <v>0.1862</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.0017</v>
+        <v>-0.9865</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.5513</v>
+        <v>-0.546</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4504</v>
+        <v>-0.4405</v>
       </c>
       <c r="P2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S2" t="n">
-        <v>2.494</v>
+        <v>1.4377</v>
       </c>
       <c r="T2" t="n">
-        <v>1.8903</v>
+        <v>1.0217</v>
       </c>
       <c r="U2" t="n">
-        <v>0.6037</v>
+        <v>0.416</v>
       </c>
       <c r="V2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="W2" t="n">
-        <v>2.1853</v>
+        <v>2.1789</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.4101</v>
+        <v>2.0137</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5989</v>
+        <v>3.117</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.1888</v>
+        <v>-1.1032</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8054</v>
+        <v>2.8039</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.1241</v>
+        <v>-0.1263</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9294</v>
+        <v>2.9301</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5643</v>
+        <v>3.5483</v>
       </c>
       <c r="K3" t="n">
-        <v>0.6163</v>
+        <v>0.6065</v>
       </c>
       <c r="L3" t="n">
-        <v>2.948</v>
+        <v>2.9417</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.759</v>
+        <v>-0.7444</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0186</v>
+        <v>-0.0116</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4633</v>
+        <v>0.1416</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5383</v>
+        <v>0.0044</v>
       </c>
       <c r="U3" t="n">
-        <v>0.075</v>
+        <v>0.1372</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W3" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.329</v>
+        <v>-1.1938</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2279</v>
+        <v>-0.0577</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.1011</v>
+        <v>-1.136</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2675</v>
+        <v>0.2685</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3638</v>
+        <v>-1.3533</v>
       </c>
       <c r="I4" t="n">
-        <v>1.6312</v>
+        <v>1.6218</v>
       </c>
       <c r="J4" t="n">
-        <v>0.6582</v>
+        <v>0.6417</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L4" t="n">
-        <v>0.5889</v>
+        <v>0.5728</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3908</v>
+        <v>-0.3733</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.433</v>
+        <v>-1.4223</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0423</v>
+        <v>1.049</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4301</v>
+        <v>0.5574</v>
       </c>
       <c r="T4" t="n">
-        <v>0.248</v>
+        <v>0.4387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1821</v>
+        <v>0.1187</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7997</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="5">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.6604</v>
+        <v>-2.5556</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5365</v>
+        <v>-1.1444</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.124</v>
+        <v>-1.4112</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.8955</v>
+        <v>-2.8934</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.3739</v>
+        <v>-0.3652</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5216</v>
+        <v>-2.5282</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9962</v>
+        <v>-1.0162</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9177999999999999</v>
+        <v>0.9136</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8993</v>
+        <v>-1.8772</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.2917</v>
+        <v>-1.2788</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6077</v>
+        <v>-0.5984</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S5" t="n">
-        <v>2.4619</v>
+        <v>1.5654</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5939</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0.868</v>
+        <v>0.5554</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. UDEZE</t>
+          <t>A. PUSTOVYI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.9226</v>
+        <v>-3.2329</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5991</v>
+        <v>-3.5141</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.3235</v>
+        <v>0.2812</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2694</v>
+        <v>-1.2482</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5195</v>
+        <v>-0.7435</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7889</v>
+        <v>-0.5047</v>
       </c>
       <c r="J6" t="n">
-        <v>1.7126</v>
+        <v>-1.0077</v>
       </c>
       <c r="K6" t="n">
-        <v>1.638</v>
+        <v>-1.0449</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0746</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.9821</v>
+        <v>-0.2405</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.1185</v>
+        <v>0.3014</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.8636</v>
+        <v>-0.5419</v>
       </c>
       <c r="P6" t="n">
-        <v>-4.083</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q6" t="n">
-        <v>-4.5367</v>
+        <v>-2.2763</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.7474</v>
+        <v>0.2916</v>
       </c>
       <c r="T6" t="n">
-        <v>2.4498</v>
+        <v>-0.2301</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2976</v>
+        <v>0.5217000000000001</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.3176</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.2249</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0927</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. PUSTOVYI</t>
+          <t>C. ORTEGA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-3.125</v>
+        <v>-3.4691</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.6147</v>
+        <v>-1.0518</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4897</v>
+        <v>-2.4174</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.249</v>
+        <v>-2.7768</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7372</v>
+        <v>-0.9625</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.5117</v>
+        <v>-1.8143</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.9986</v>
+        <v>-1.0167</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0359</v>
+        <v>-0.7035</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0373</v>
+        <v>-0.3132</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2504</v>
+        <v>-1.7601</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2986</v>
+        <v>-0.259</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.549</v>
+        <v>-1.5011</v>
       </c>
       <c r="P7" t="n">
-        <v>-2.2683</v>
+        <v>0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.2683</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>0.6829</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3923</v>
+        <v>0.2589</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3478</v>
+        <v>-0.0351</v>
       </c>
       <c r="U7" t="n">
-        <v>0.7401</v>
+        <v>0.294</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ORTEGA</t>
+          <t>A. BEST</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-4.2305</v>
+        <v>-3.7145</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.6298</v>
+        <v>-3.8858</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.6007</v>
+        <v>0.1713</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.7835</v>
+        <v>-4.4934</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.9683</v>
+        <v>-1.6827</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.8152</v>
+        <v>-2.8107</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0037</v>
+        <v>-3.0954</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.6998</v>
+        <v>-1.9552</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.3039</v>
+        <v>-1.1401</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.7798</v>
+        <v>-1.3981</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2685</v>
+        <v>0.2725</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.5113</v>
+        <v>-1.6706</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6805</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4884</v>
+        <v>0.6911</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6261</v>
+        <v>0.0322</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1376</v>
+        <v>0.6589</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.639</v>
+        <v>0.3155</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.639</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. BEST</t>
+          <t>F. BASSAS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.3287</v>
+        <v>-4.4491</v>
       </c>
       <c r="E9" t="n">
-        <v>-4.6308</v>
+        <v>-2.9837</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3021</v>
+        <v>-1.4654</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.4914</v>
+        <v>-1.3377</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6766</v>
+        <v>-1.3184</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.8148</v>
+        <v>-0.0193</v>
       </c>
       <c r="J9" t="n">
-        <v>-3.0711</v>
+        <v>-0.7352</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.9435</v>
+        <v>-0.7724</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.1276</v>
+        <v>0.0372</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.4203</v>
+        <v>-0.6025</v>
       </c>
       <c r="N9" t="n">
-        <v>0.2669</v>
+        <v>-0.546</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.6871</v>
+        <v>-0.0565</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.2268</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.2276</v>
       </c>
       <c r="S9" t="n">
-        <v>0.068</v>
+        <v>0.0267</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.747</v>
+        <v>0.0278</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8151</v>
+        <v>-0.0011</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3214</v>
+        <v>-1.0895</v>
       </c>
       <c r="W9" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>F. BASSAS</t>
+          <t>M. UDEZE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.7792</v>
+        <v>-4.7069</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.2087</v>
+        <v>-2.2806</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.5704</v>
+        <v>-2.4263</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.3416</v>
+        <v>-0.2662</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.3203</v>
+        <v>0.5171</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0213</v>
+        <v>-0.7833</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.7317</v>
+        <v>1.698</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.769</v>
+        <v>1.6235</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0373</v>
+        <v>0.0745</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6099</v>
+        <v>-1.9642</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5513</v>
+        <v>-1.1064</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0586</v>
+        <v>-0.8578</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.0415</v>
+        <v>-4.0974</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.2683</v>
+        <v>-4.5526</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.3033</v>
+        <v>0.9754</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.2087</v>
+        <v>0.8033</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.09470000000000001</v>
+        <v>0.1721</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.0927</v>
+        <v>-1.3187</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.2292</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Y. PONS</t>
+          <t>K. KURIC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.9416</v>
+        <v>-4.8072</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.9346</v>
+        <v>-2.88</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0069</v>
+        <v>-1.9272</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4034</v>
+        <v>-3.5921</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0244</v>
+        <v>-3.248</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.4278</v>
+        <v>-0.3441</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.0686</v>
+        <v>-1.1281</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1039</v>
+        <v>-1.9692</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.1725</v>
+        <v>0.8411</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.3348</v>
+        <v>-2.464</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0795</v>
+        <v>-1.2788</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.2554</v>
+        <v>-1.1852</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1342</v>
+        <v>0.6829</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3257</v>
+        <v>0.9231</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0393</v>
+        <v>0.5245</v>
       </c>
       <c r="U11" t="n">
-        <v>0.2864</v>
+        <v>0.3986</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8639</v>
+        <v>-0.5447</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.7712</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>K. KURIC</t>
+          <t>Y. PONS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.7284</v>
+        <v>-4.8839</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.5535</v>
+        <v>-3.9987</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.1749</v>
+        <v>-0.8852</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.5861</v>
+        <v>-3.3933</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.2422</v>
+        <v>0.0312</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3439</v>
+        <v>-3.4245</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.0977</v>
+        <v>-2.0793</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.9506</v>
+        <v>0.1034</v>
       </c>
       <c r="L12" t="n">
-        <v>0.8529</v>
+        <v>-2.1827</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.4884</v>
+        <v>-1.3139</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.2917</v>
+        <v>-0.0722</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.1967</v>
+        <v>-1.2417</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.5878</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>0.6805</v>
+        <v>1.1382</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.3728</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1875</v>
+        <v>-0.0073</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1793</v>
+        <v>0.3801</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5463</v>
+        <v>-1.8634</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.7739</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5463</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.486599999999999</v>
+        <v>-8.713900000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.2513</v>
+        <v>-4.9476</v>
       </c>
       <c r="F13" t="n">
-        <v>-4.2352</v>
+        <v>-3.7663</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.4901</v>
+        <v>-4.4991</v>
       </c>
       <c r="H13" t="n">
-        <v>-3.1094</v>
+        <v>-3.1213</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.3807</v>
+        <v>-1.3778</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.2358</v>
+        <v>-2.268</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.014</v>
+        <v>-3.0347</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7782</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-2.2543</v>
+        <v>-2.231</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.0954</v>
+        <v>-0.0866</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.159</v>
+        <v>-2.1444</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.3098</v>
+        <v>-4.325</v>
       </c>
       <c r="Q13" t="n">
-        <v>-4.5367</v>
+        <v>-4.5526</v>
       </c>
       <c r="R13" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1403</v>
+        <v>0.6549</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1179</v>
+        <v>0.2388</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0224</v>
+        <v>0.416</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W13" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-32.0887</v>
+        <v>-31.7425</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.291</v>
+        <v>-16.2244</v>
       </c>
       <c r="F14" t="n">
-        <v>-15.7976</v>
+        <v>-15.518</v>
       </c>
       <c r="G14" t="n">
-        <v>-18.2174</v>
+        <v>-18.2119</v>
       </c>
       <c r="H14" t="n">
-        <v>-8.888400000000001</v>
+        <v>-8.902700000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.3291</v>
+        <v>-9.3093</v>
       </c>
       <c r="J14" t="n">
-        <v>-2.0469</v>
+        <v>-2.256200000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.0327</v>
+        <v>-2.1478</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.01419999999999977</v>
+        <v>-0.1085000000000003</v>
       </c>
       <c r="M14" t="n">
-        <v>-16.1708</v>
+        <v>-15.9557</v>
       </c>
       <c r="N14" t="n">
-        <v>-6.855800000000002</v>
+        <v>-6.754999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>-9.315100000000001</v>
+        <v>-9.200700000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>-13.6098</v>
+        <v>-13.6578</v>
       </c>
       <c r="Q14" t="n">
-        <v>-21.5493</v>
+        <v>-21.6251</v>
       </c>
       <c r="R14" t="n">
-        <v>7.9392</v>
+        <v>7.9672</v>
       </c>
       <c r="S14" t="n">
-        <v>7.515900000000001</v>
+        <v>7.896599999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>3.448</v>
+        <v>3.8289</v>
       </c>
       <c r="U14" t="n">
-        <v>4.0678</v>
+        <v>4.067600000000001</v>
       </c>
       <c r="V14" t="n">
-        <v>-7.777100000000001</v>
+        <v>-7.769199999999999</v>
       </c>
       <c r="W14" t="n">
-        <v>3.8567</v>
+        <v>3.828</v>
       </c>
       <c r="X14" t="n">
-        <v>-11.6337</v>
+        <v>-11.5972</v>
       </c>
     </row>
     <row r="15">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>10.7141</v>
+        <v>9.3942</v>
       </c>
       <c r="E15" t="n">
-        <v>5.7638</v>
+        <v>5.2593</v>
       </c>
       <c r="F15" t="n">
-        <v>4.9502</v>
+        <v>4.1349</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9105</v>
+        <v>3.9112</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0015</v>
+        <v>2.9932</v>
       </c>
       <c r="I15" t="n">
-        <v>0.909</v>
+        <v>0.918</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0967</v>
+        <v>3.0763</v>
       </c>
       <c r="K15" t="n">
-        <v>2.7982</v>
+        <v>2.7784</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2985</v>
+        <v>0.2979</v>
       </c>
       <c r="M15" t="n">
-        <v>0.8138</v>
+        <v>0.8349</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2033</v>
+        <v>0.2148</v>
       </c>
       <c r="O15" t="n">
-        <v>0.6105</v>
+        <v>0.6201</v>
       </c>
       <c r="P15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>3.1757</v>
+        <v>3.1868</v>
       </c>
       <c r="S15" t="n">
-        <v>1.1211</v>
+        <v>-0.1983</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1603</v>
+        <v>-0.3115</v>
       </c>
       <c r="U15" t="n">
-        <v>0.9608</v>
+        <v>0.1132</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="W15" t="n">
-        <v>2.5068</v>
+        <v>2.4945</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>7.5592</v>
+        <v>7.8243</v>
       </c>
       <c r="E16" t="n">
-        <v>5.0315</v>
+        <v>5.334</v>
       </c>
       <c r="F16" t="n">
-        <v>2.5277</v>
+        <v>2.4903</v>
       </c>
       <c r="G16" t="n">
-        <v>3.9717</v>
+        <v>3.9564</v>
       </c>
       <c r="H16" t="n">
-        <v>4.0677</v>
+        <v>4.0642</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0961</v>
+        <v>-0.1078</v>
       </c>
       <c r="J16" t="n">
-        <v>3.3152</v>
+        <v>3.2795</v>
       </c>
       <c r="K16" t="n">
-        <v>3.5499</v>
+        <v>3.5336</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.2347</v>
+        <v>-0.2541</v>
       </c>
       <c r="M16" t="n">
-        <v>0.6565</v>
+        <v>0.677</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5178</v>
+        <v>0.5306</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1387</v>
+        <v>0.1463</v>
       </c>
       <c r="P16" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R16" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.9173</v>
+        <v>-0.6282</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9739</v>
+        <v>-0.6205000000000001</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0565</v>
+        <v>-0.0077</v>
       </c>
       <c r="V16" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="W16" t="n">
-        <v>3.8243</v>
+        <v>3.8132</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>5.6992</v>
+        <v>5.3881</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0288</v>
+        <v>1.5344</v>
       </c>
       <c r="F17" t="n">
-        <v>3.6704</v>
+        <v>3.8538</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5751</v>
+        <v>3.5806</v>
       </c>
       <c r="H17" t="n">
-        <v>0.2913</v>
+        <v>0.3038</v>
       </c>
       <c r="I17" t="n">
-        <v>3.2839</v>
+        <v>3.2768</v>
       </c>
       <c r="J17" t="n">
-        <v>2.1882</v>
+        <v>2.1733</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1039</v>
+        <v>0.1034</v>
       </c>
       <c r="L17" t="n">
-        <v>2.0843</v>
+        <v>2.0699</v>
       </c>
       <c r="M17" t="n">
-        <v>1.3869</v>
+        <v>1.4073</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O17" t="n">
-        <v>1.1995</v>
+        <v>1.2069</v>
       </c>
       <c r="P17" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R17" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.2616</v>
+        <v>-0.5794</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1179</v>
+        <v>-0.5903</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1437</v>
+        <v>0.0108</v>
       </c>
       <c r="V17" t="n">
-        <v>1.4783</v>
+        <v>1.4764</v>
       </c>
       <c r="W17" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3856</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="18">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>4.7322</v>
+        <v>4.8143</v>
       </c>
       <c r="E18" t="n">
-        <v>2.7163</v>
+        <v>2.8088</v>
       </c>
       <c r="F18" t="n">
-        <v>2.0159</v>
+        <v>2.0055</v>
       </c>
       <c r="G18" t="n">
-        <v>4.493</v>
+        <v>4.4879</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0779</v>
+        <v>-1.0771</v>
       </c>
       <c r="I18" t="n">
-        <v>5.5709</v>
+        <v>5.5649</v>
       </c>
       <c r="J18" t="n">
-        <v>4.407</v>
+        <v>4.3861</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.9666</v>
+        <v>-0.976</v>
       </c>
       <c r="L18" t="n">
-        <v>5.3736</v>
+        <v>5.3621</v>
       </c>
       <c r="M18" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.1018</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1113</v>
+        <v>-0.1011</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1973</v>
+        <v>0.2028</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.6681</v>
+        <v>-0.5841</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5565</v>
+        <v>-0.4392</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1116</v>
+        <v>-0.1449</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>4.59</v>
+        <v>4.0193</v>
       </c>
       <c r="E19" t="n">
-        <v>1.8888</v>
+        <v>1.5089</v>
       </c>
       <c r="F19" t="n">
-        <v>2.7012</v>
+        <v>2.5104</v>
       </c>
       <c r="G19" t="n">
-        <v>2.1268</v>
+        <v>2.1155</v>
       </c>
       <c r="H19" t="n">
-        <v>0.9754</v>
+        <v>0.9765</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1514</v>
+        <v>1.139</v>
       </c>
       <c r="J19" t="n">
-        <v>1.9372</v>
+        <v>1.911</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L19" t="n">
-        <v>1.8577</v>
+        <v>1.8388</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1896</v>
+        <v>0.2044</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8959</v>
+        <v>0.9043</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7063</v>
+        <v>-0.6998</v>
       </c>
       <c r="P19" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>2.722</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0626</v>
+        <v>-0.5122</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.0484</v>
+        <v>-0.4021</v>
       </c>
       <c r="U19" t="n">
-        <v>0.111</v>
+        <v>-0.11</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.3214</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>W. VAN BECK</t>
+          <t>B. FITIPALDO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3973</v>
+        <v>2.0915</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7066</v>
+        <v>0.5351</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3093</v>
+        <v>1.5565</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3491</v>
+        <v>2.2563</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.176</v>
+        <v>1.4614</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5251</v>
+        <v>0.7949000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>1.2763</v>
+        <v>0.6318</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0448</v>
+        <v>0.9308</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2315</v>
+        <v>-0.299</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9272</v>
+        <v>1.6245</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2209</v>
+        <v>0.5306</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.7063</v>
+        <v>1.0939</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>2.5039</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8837</v>
+        <v>-0.8768</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.2087</v>
+        <v>-0.6415</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.6751</v>
+        <v>-0.2353</v>
       </c>
       <c r="V20" t="n">
-        <v>1.4783</v>
+        <v>-1.792</v>
       </c>
       <c r="W20" t="n">
-        <v>1.639</v>
+        <v>0.5447</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-2.3367</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. ABROMAITIS</t>
+          <t>W. VAN BECK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.3648</v>
+        <v>1.7346</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.4385</v>
+        <v>2.8101</v>
       </c>
       <c r="F21" t="n">
-        <v>1.8033</v>
+        <v>-1.0755</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1677</v>
+        <v>0.351</v>
       </c>
       <c r="H21" t="n">
-        <v>1.2712</v>
+        <v>-0.178</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.1035</v>
+        <v>0.529</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4658</v>
+        <v>1.2665</v>
       </c>
       <c r="K21" t="n">
-        <v>1.1775</v>
+        <v>0.0377</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.7117</v>
+        <v>1.2288</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2981</v>
+        <v>-0.9155</v>
       </c>
       <c r="N21" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.2157</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.3918</v>
+        <v>-0.6998</v>
       </c>
       <c r="P21" t="n">
-        <v>0.6805</v>
+        <v>0.4553</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.8147</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2547</v>
+        <v>-0.5481</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2299</v>
+        <v>-0.0907</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4845</v>
+        <v>-0.4575</v>
       </c>
       <c r="V21" t="n">
-        <v>0.7712</v>
+        <v>1.4764</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>1.6342</v>
       </c>
       <c r="X21" t="n">
-        <v>0.7712</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>B. FITIPALDO</t>
+          <t>T. ABROMAITIS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>1.2038</v>
+        <v>1.3582</v>
       </c>
       <c r="E22" t="n">
-        <v>0.09370000000000001</v>
+        <v>-0.6861</v>
       </c>
       <c r="F22" t="n">
-        <v>1.1101</v>
+        <v>2.0443</v>
       </c>
       <c r="G22" t="n">
-        <v>2.2605</v>
+        <v>0.1731</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4529</v>
+        <v>1.2723</v>
       </c>
       <c r="I22" t="n">
-        <v>0.8076</v>
+        <v>-1.0991</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6604</v>
+        <v>0.4569</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9351</v>
+        <v>1.1721</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.2747</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>1.6001</v>
+        <v>-0.2838</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5178</v>
+        <v>0.1002</v>
       </c>
       <c r="O22" t="n">
-        <v>1.0823</v>
+        <v>-0.384</v>
       </c>
       <c r="P22" t="n">
-        <v>2.4952</v>
+        <v>0.6829</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>2.4952</v>
+        <v>1.8211</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.7521</v>
+        <v>-0.2717</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.113</v>
+        <v>-0.0049</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6391</v>
+        <v>-0.2669</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.7997</v>
+        <v>0.7739</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5463</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-2.3461</v>
+        <v>0.7739</v>
       </c>
     </row>
     <row r="23">
@@ -2203,64 +2203,64 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1659</v>
+        <v>0.3048</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.4642</v>
+        <v>-0.7271</v>
       </c>
       <c r="F23" t="n">
-        <v>0.6301</v>
+        <v>1.0319</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3924</v>
+        <v>-1.3887</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.5181</v>
+        <v>-0.5143</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8743</v>
+        <v>-0.8744</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.1294</v>
+        <v>-1.1486</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.0764</v>
+        <v>-0.0829</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.053</v>
+        <v>-1.0656</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.263</v>
+        <v>-0.2402</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1787</v>
+        <v>0.1912</v>
       </c>
       <c r="P23" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.5344</v>
+        <v>-0.3959</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1603</v>
+        <v>-0.0746</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6947</v>
+        <v>-0.3213</v>
       </c>
       <c r="V23" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W23" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.3823</v>
+        <v>-1.0532</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6324</v>
+        <v>0.9768</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0147</v>
+        <v>-2.0299</v>
       </c>
       <c r="G24" t="n">
         <v>0.0689</v>
       </c>
       <c r="H24" t="n">
-        <v>0.6047</v>
+        <v>0.6005</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.5357</v>
+        <v>-0.5316</v>
       </c>
       <c r="J24" t="n">
-        <v>0.4339</v>
+        <v>0.4252</v>
       </c>
       <c r="K24" t="n">
-        <v>0.3219</v>
+        <v>0.3135</v>
       </c>
       <c r="L24" t="n">
-        <v>0.112</v>
+        <v>0.1117</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.3649</v>
+        <v>-0.3563</v>
       </c>
       <c r="N24" t="n">
-        <v>0.2828</v>
+        <v>0.287</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6433</v>
       </c>
       <c r="P24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.4927</v>
+        <v>-0.1707</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1449</v>
+        <v>-0.1775</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.639</v>
+        <v>-1.6342</v>
       </c>
       <c r="W24" t="n">
-        <v>0.5463</v>
+        <v>0.5447</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="25">
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-1.6955</v>
+        <v>-1.2318</v>
       </c>
       <c r="E25" t="n">
-        <v>-1.6754</v>
+        <v>-1.5693</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0201</v>
+        <v>0.3375</v>
       </c>
       <c r="G25" t="n">
-        <v>0.0454</v>
+        <v>0.0504</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0693</v>
+        <v>-0.0689</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J25" t="n">
-        <v>0.0848</v>
+        <v>0.07770000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>0.0102</v>
+        <v>0.0033</v>
       </c>
       <c r="L25" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.0395</v>
+        <v>-0.0273</v>
       </c>
       <c r="N25" t="n">
-        <v>-0.0795</v>
+        <v>-0.0722</v>
       </c>
       <c r="O25" t="n">
-        <v>0.04</v>
+        <v>0.0449</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q25" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R25" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0604</v>
+        <v>-0.5993000000000001</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6261</v>
+        <v>-0.5089</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.4343</v>
+        <v>-0.09039999999999999</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-2.26</v>
+        <v>-1.7639</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.3256</v>
+        <v>-2.1088</v>
       </c>
       <c r="F26" t="n">
-        <v>0.06569999999999999</v>
+        <v>0.345</v>
       </c>
       <c r="G26" t="n">
-        <v>-1.3589</v>
+        <v>-1.3507</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.9351</v>
+        <v>-0.9308</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4238</v>
+        <v>-0.4199</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.5654</v>
+        <v>-0.5802</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.1225</v>
+        <v>-1.1311</v>
       </c>
       <c r="L26" t="n">
-        <v>0.5570000000000001</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.7935</v>
+        <v>-0.7704</v>
       </c>
       <c r="N26" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O26" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P26" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="Q26" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R26" t="n">
-        <v>2.2683</v>
+        <v>2.2763</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.8745</v>
+        <v>-1.3936</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.6261</v>
+        <v>-0.3904</v>
       </c>
       <c r="U26" t="n">
-        <v>-1.2485</v>
+        <v>-1.0031</v>
       </c>
       <c r="V26" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="27">
@@ -2515,67 +2515,67 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>32.0887</v>
+        <v>32.8804</v>
       </c>
       <c r="E27" t="n">
-        <v>15.9582</v>
+        <v>15.6761</v>
       </c>
       <c r="F27" t="n">
-        <v>16.1305</v>
+        <v>17.2047</v>
       </c>
       <c r="G27" t="n">
-        <v>18.2174</v>
+        <v>18.2119</v>
       </c>
       <c r="H27" t="n">
-        <v>8.888299999999999</v>
+        <v>8.902800000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>9.3292</v>
+        <v>9.309200000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>16.1707</v>
+        <v>15.9555</v>
       </c>
       <c r="K27" t="n">
-        <v>6.855500000000001</v>
+        <v>6.754999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>9.315100000000001</v>
+        <v>9.200700000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>2.0467</v>
+        <v>2.2564</v>
       </c>
       <c r="N27" t="n">
-        <v>2.0327</v>
+        <v>2.147699999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>0.0141</v>
+        <v>0.1083999999999999</v>
       </c>
       <c r="P27" t="n">
-        <v>13.6101</v>
+        <v>13.6579</v>
       </c>
       <c r="Q27" t="n">
-        <v>-7.9394</v>
+        <v>-7.967400000000001</v>
       </c>
       <c r="R27" t="n">
-        <v>21.5493</v>
+        <v>21.6251</v>
       </c>
       <c r="S27" t="n">
-        <v>-7.5158</v>
+        <v>-6.758300000000001</v>
       </c>
       <c r="T27" t="n">
-        <v>-4.0679</v>
+        <v>-4.0678</v>
       </c>
       <c r="U27" t="n">
-        <v>-3.4481</v>
+        <v>-2.6906</v>
       </c>
       <c r="V27" t="n">
-        <v>7.777099999999998</v>
+        <v>7.769100000000002</v>
       </c>
       <c r="W27" t="n">
-        <v>11.7944</v>
+        <v>11.755</v>
       </c>
       <c r="X27" t="n">
-        <v>-4.0174</v>
+        <v>-3.9858</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104469_W2.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104469_W2.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X27"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-11.5972</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-2.3367</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0.7739</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,11 @@
       <c r="X26" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_104469_W2.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2577,6 +2703,7 @@
       <c r="X27" t="n">
         <v>-3.9858</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
